--- a/src/test/java/TestData/DataInput.xlsx
+++ b/src/test/java/TestData/DataInput.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2480119\IdeaProjects\Automation\src\test\java\TestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
   <si>
     <t>password</t>
   </si>
@@ -84,12 +84,25 @@
   </si>
   <si>
     <t>virat</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Invalid name""</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>123456789 doesn't match 12345678</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -99,12 +112,32 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -119,8 +152,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,157 +497,193 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="15.6328125" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" customWidth="1"/>
-    <col min="5" max="5" width="17.6328125" customWidth="1"/>
-    <col min="6" max="6" width="29.1796875" customWidth="1"/>
-    <col min="7" max="7" width="48.453125" customWidth="1"/>
+    <col min="3" max="3" customWidth="true" width="15.6328125"/>
+    <col min="4" max="4" customWidth="true" width="12.26953125"/>
+    <col min="5" max="5" customWidth="true" width="17.6328125"/>
+    <col min="6" max="6" customWidth="true" width="29.1796875"/>
+    <col min="7" max="7" customWidth="true" width="48.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>66333822</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>123456789</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <v>123456789</v>
       </c>
-      <c r="F2" t="s">
-        <v>12</v>
+      <c r="F2" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s" s="1">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>242526272</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <v>12345667</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <v>3456886</v>
       </c>
-      <c r="F3" t="s">
-        <v>12</v>
+      <c r="F3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>4263738338</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0">
         <v>123456789</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="0">
         <v>123456789</v>
       </c>
-      <c r="F4" t="s">
-        <v>12</v>
+      <c r="F4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0">
         <v>66333822</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <v>123456789</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="0">
         <v>123456789</v>
       </c>
-      <c r="F5" t="s">
-        <v>12</v>
+      <c r="F5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s" s="4">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <v>242526272</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0">
         <v>12345667</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <v>3456886</v>
       </c>
-      <c r="F6" t="s">
-        <v>12</v>
+      <c r="F6" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s" s="5">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0">
         <v>4263738338</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="0">
         <v>123456789</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="0">
         <v>12345678</v>
       </c>
-      <c r="F7" t="s">
-        <v>12</v>
+      <c r="F7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="6">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/java/TestData/DataInput.xlsx
+++ b/src/test/java/TestData/DataInput.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2480119\IdeaProjects\Automation\src\test\java\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2480119\IdeaProjects\OpenCart\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5622006-FEAF-4895-AC35-85498233DD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350D22A7-E86F-4DCC-AD47-43ACD4DEEA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A8A0D7BE-DABA-44A9-8673-104FEFB7AEA8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
   <si>
     <t>password</t>
   </si>
@@ -71,31 +71,25 @@
     <t>Actual</t>
   </si>
   <si>
-    <t>""</t>
+    <t xml:space="preserve"> " "</t>
   </si>
   <si>
     <t>Your Account Has Been Created!</t>
   </si>
   <si>
-    <t>abhisekh</t>
-  </si>
-  <si>
     <t>Krish</t>
   </si>
   <si>
-    <t>virat</t>
-  </si>
-  <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>Invalid name""</t>
+    <t>3456789 doesn't match 342216789</t>
   </si>
   <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>123456789 doesn't match 12345678</t>
+    <t>Invalid name " "</t>
   </si>
 </sst>
 </file>
@@ -120,22 +114,22 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
       <patternFill patternType="none">
         <fgColor indexed="17"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
       <patternFill patternType="none">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="10"/>
       </patternFill>
     </fill>
@@ -152,14 +146,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,14 +493,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72CCD448-5E3A-4C2E-ADD6-9E13D3F5338E}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" customWidth="true" width="15.6328125"/>
     <col min="4" max="4" customWidth="true" width="12.26953125"/>
     <col min="5" max="5" customWidth="true" width="17.6328125"/>
     <col min="6" max="6" customWidth="true" width="29.1796875"/>
-    <col min="7" max="7" customWidth="true" width="48.453125"/>
+    <col min="7" max="7" customWidth="true" width="37.36328125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -530,7 +529,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>7</v>
       </c>
@@ -541,10 +540,10 @@
         <v>66333822</v>
       </c>
       <c r="D2" s="0">
-        <v>123456789</v>
+        <v>1234569</v>
       </c>
       <c r="E2" s="0">
-        <v>123456789</v>
+        <v>1234569</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>12</v>
@@ -552,138 +551,60 @@
       <c r="G2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="H2" t="s" s="1">
-        <v>16</v>
+      <c r="H2" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" s="0">
-        <v>242526272</v>
+        <v>6633383222</v>
       </c>
       <c r="D3" s="0">
-        <v>12345667</v>
+        <v>3456789</v>
       </c>
       <c r="E3" s="0">
-        <v>3456886</v>
+        <v>342216789</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>12</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" s="0">
-        <v>4263738338</v>
+        <v>242526272</v>
       </c>
       <c r="D4" s="0">
-        <v>123456789</v>
+        <v>12345667</v>
       </c>
       <c r="E4" s="0">
-        <v>123456789</v>
+        <v>3456886</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>12</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="H4" t="s" s="3">
+        <v>17</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C5" s="0">
-        <v>66333822</v>
-      </c>
-      <c r="D5" s="0">
-        <v>123456789</v>
-      </c>
-      <c r="E5" s="0">
-        <v>123456789</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="H5" t="s" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="C6" s="0">
-        <v>242526272</v>
-      </c>
-      <c r="D6" s="0">
-        <v>12345667</v>
-      </c>
-      <c r="E6" s="0">
-        <v>3456886</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C7" s="0">
-        <v>4263738338</v>
-      </c>
-      <c r="D7" s="0">
-        <v>123456789</v>
-      </c>
-      <c r="E7" s="0">
-        <v>12345678</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s" s="6">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
